--- a/data/xlsx/bwcci--graphic-design-ad-entrepreneurship-development.xlsx
+++ b/data/xlsx/bwcci--graphic-design-ad-entrepreneurship-development.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,7 +640,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -645,7 +651,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -656,7 +664,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -667,7 +675,9 @@
       <c r="C17" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -678,7 +688,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -689,7 +699,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -700,7 +712,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -711,7 +723,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -722,7 +736,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -733,7 +747,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -744,7 +760,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -755,7 +771,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -766,7 +784,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -777,7 +795,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -788,7 +808,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -799,7 +819,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -810,7 +832,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -821,7 +843,9 @@
       <c r="C24" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -832,7 +856,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -840,18 +864,18 @@
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="10">
+      <c r="E25" s="15">
         <f>SUM(E16:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="15">
         <f>SUM(F16:F24)</f>
         <v/>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -860,7 +884,7 @@
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="12" t="n"/>
-      <c r="F26" s="10">
+      <c r="F26" s="15">
         <f>F25/E25*100</f>
         <v/>
       </c>
@@ -868,7 +892,7 @@
     </row>
     <row r="27" ht="9.75" customHeight="1"/>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -877,11 +901,11 @@
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10">
+      <c r="F28" s="15">
         <f>F26*30/100</f>
         <v/>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
